--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/54.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/54.xlsx
@@ -426,13 +426,13 @@
         <v>-2.905969466823066</v>
       </c>
       <c r="E2">
-        <v>-4.650359962294407</v>
+        <v>-5.392957243968223</v>
       </c>
       <c r="F2">
-        <v>-6.458758796905748</v>
+        <v>-7.207015498185255</v>
       </c>
       <c r="G2">
-        <v>0.8049877921153087</v>
+        <v>0.5816881849459278</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.102287889129228</v>
       </c>
       <c r="E3">
-        <v>-4.017582703780605</v>
+        <v>-5.345978854612651</v>
       </c>
       <c r="F3">
-        <v>-6.883216133758731</v>
+        <v>-6.935108633636977</v>
       </c>
       <c r="G3">
-        <v>1.225996489435504</v>
+        <v>0.5336753429898778</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.372392557022132</v>
       </c>
       <c r="E4">
-        <v>-4.431924490060419</v>
+        <v>-6.471594467855225</v>
       </c>
       <c r="F4">
-        <v>-7.136702518878053</v>
+        <v>-7.023235533007521</v>
       </c>
       <c r="G4">
-        <v>0.7563558781434149</v>
+        <v>1.33979980289349</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-0.8341118822562079</v>
       </c>
       <c r="E5">
-        <v>-5.199899340073221</v>
+        <v>-6.370220048719517</v>
       </c>
       <c r="F5">
-        <v>-7.010162832528526</v>
+        <v>-7.411136978067372</v>
       </c>
       <c r="G5">
-        <v>1.582105252003827</v>
+        <v>1.040612560327396</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-0.4671286406093953</v>
       </c>
       <c r="E6">
-        <v>-6.004889936624719</v>
+        <v>-6.96262143298093</v>
       </c>
       <c r="F6">
-        <v>-6.813869610986426</v>
+        <v>-7.54156941355705</v>
       </c>
       <c r="G6">
-        <v>1.376947434389652</v>
+        <v>0.1253990038137194</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.2786735059046191</v>
       </c>
       <c r="E7">
-        <v>-7.033573563733109</v>
+        <v>-7.822782428367876</v>
       </c>
       <c r="F7">
-        <v>-6.948300903912588</v>
+        <v>-7.08709015959156</v>
       </c>
       <c r="G7">
-        <v>0.9850152585408758</v>
+        <v>0.5021986760024874</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.2382964018665084</v>
       </c>
       <c r="E8">
-        <v>-6.942990498157679</v>
+        <v>-8.847625909517761</v>
       </c>
       <c r="F8">
-        <v>-6.758276782236755</v>
+        <v>-7.082269358784963</v>
       </c>
       <c r="G8">
-        <v>1.879504799978715</v>
+        <v>0.07557860399322729</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3213617281039137</v>
       </c>
       <c r="E9">
-        <v>-8.654454793772567</v>
+        <v>-9.317446030865547</v>
       </c>
       <c r="F9">
-        <v>-7.064504137678521</v>
+        <v>-7.458766141621256</v>
       </c>
       <c r="G9">
-        <v>0.8614425251965002</v>
+        <v>-0.2380823436705606</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.4838965302488967</v>
       </c>
       <c r="E10">
-        <v>-9.714534331176138</v>
+        <v>-9.581342853662537</v>
       </c>
       <c r="F10">
-        <v>-6.9920864132097</v>
+        <v>-6.947893099639362</v>
       </c>
       <c r="G10">
-        <v>0.5809400016540526</v>
+        <v>-0.1506773203427227</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.6854050735714067</v>
       </c>
       <c r="E11">
-        <v>-9.379463482400592</v>
+        <v>-10.92076583870326</v>
       </c>
       <c r="F11">
-        <v>-6.429726695990391</v>
+        <v>-6.985342201568801</v>
       </c>
       <c r="G11">
-        <v>0.8877050829595385</v>
+        <v>-0.9028465090472935</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.8842406229934079</v>
       </c>
       <c r="E12">
-        <v>-10.03383250498297</v>
+        <v>-11.08670271176632</v>
       </c>
       <c r="F12">
-        <v>-6.723970940622984</v>
+        <v>-6.717862190980656</v>
       </c>
       <c r="G12">
-        <v>1.142984560038279</v>
+        <v>-0.304899084289671</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-1.042736169340785</v>
       </c>
       <c r="E13">
-        <v>-11.38540538578627</v>
+        <v>-12.37968166738438</v>
       </c>
       <c r="F13">
-        <v>-6.252529404450181</v>
+        <v>-6.628402999008749</v>
       </c>
       <c r="G13">
-        <v>0.7706210188721344</v>
+        <v>0.2693845609532411</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.13504772067625</v>
       </c>
       <c r="E14">
-        <v>-11.51555372876672</v>
+        <v>-13.63002956869423</v>
       </c>
       <c r="F14">
-        <v>-5.993473917479216</v>
+        <v>-6.236018478428767</v>
       </c>
       <c r="G14">
-        <v>1.298431225834758</v>
+        <v>-0.0244991876589407</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.146618028375894</v>
       </c>
       <c r="E15">
-        <v>-12.23062694542191</v>
+        <v>-13.1607755065974</v>
       </c>
       <c r="F15">
-        <v>-6.122416085702465</v>
+        <v>-6.162374569654918</v>
       </c>
       <c r="G15">
-        <v>1.471268187349028</v>
+        <v>-0.3438807580145892</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.080082038367756</v>
       </c>
       <c r="E16">
-        <v>-12.80835154542446</v>
+        <v>-13.26397037228419</v>
       </c>
       <c r="F16">
-        <v>-5.370509734140828</v>
+        <v>-5.89145395796548</v>
       </c>
       <c r="G16">
-        <v>1.470096254228126</v>
+        <v>1.053123111920302</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.9575132351261708</v>
       </c>
       <c r="E17">
-        <v>-13.87487510134095</v>
+        <v>-15.22924205060698</v>
       </c>
       <c r="F17">
-        <v>-5.193328675586251</v>
+        <v>-5.686024336997209</v>
       </c>
       <c r="G17">
-        <v>2.06971550448308</v>
+        <v>2.118036227174283</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.8134173934131691</v>
       </c>
       <c r="E18">
-        <v>-13.73386747769011</v>
+        <v>-14.26325514613479</v>
       </c>
       <c r="F18">
-        <v>-5.043577403487085</v>
+        <v>-5.332637782731967</v>
       </c>
       <c r="G18">
-        <v>1.922982194545964</v>
+        <v>1.672453350316077</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.6930837156852575</v>
       </c>
       <c r="E19">
-        <v>-15.69456539726515</v>
+        <v>-16.87641107226097</v>
       </c>
       <c r="F19">
-        <v>-4.644738489448731</v>
+        <v>-5.189466808711452</v>
       </c>
       <c r="G19">
-        <v>1.984161076111695</v>
+        <v>2.03732843747239</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.6389936110538105</v>
       </c>
       <c r="E20">
-        <v>-16.32260587196693</v>
+        <v>-17.50340546946698</v>
       </c>
       <c r="F20">
-        <v>-4.556168152421864</v>
+        <v>-4.457632345922095</v>
       </c>
       <c r="G20">
-        <v>2.28193471573252</v>
+        <v>1.715708938332194</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.6848516399511073</v>
       </c>
       <c r="E21">
-        <v>-16.41957408589317</v>
+        <v>-18.59975808367198</v>
       </c>
       <c r="F21">
-        <v>-3.912500973503894</v>
+        <v>-4.781570680542699</v>
       </c>
       <c r="G21">
-        <v>2.645108182481648</v>
+        <v>1.593543186842009</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.8541504092198827</v>
       </c>
       <c r="E22">
-        <v>-17.02590958467619</v>
+        <v>-19.09829325870241</v>
       </c>
       <c r="F22">
-        <v>-3.67490232612826</v>
+        <v>-3.999177990108853</v>
       </c>
       <c r="G22">
-        <v>2.064726512355398</v>
+        <v>1.556630604079135</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-1.148060819577274</v>
       </c>
       <c r="E23">
-        <v>-17.7403986281844</v>
+        <v>-20.21457115854117</v>
       </c>
       <c r="F23">
-        <v>-3.439397337972837</v>
+        <v>-4.150137629821499</v>
       </c>
       <c r="G23">
-        <v>2.187527888589124</v>
+        <v>0.8490346005153118</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.555361179334179</v>
       </c>
       <c r="E24">
-        <v>-18.14839602237947</v>
+        <v>-19.86819723864247</v>
       </c>
       <c r="F24">
-        <v>-3.027560157633513</v>
+        <v>-4.096494343053734</v>
       </c>
       <c r="G24">
-        <v>1.403931691080252</v>
+        <v>1.534929978069213</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-2.048013736501146</v>
       </c>
       <c r="E25">
-        <v>-18.97463874744896</v>
+        <v>-20.34371418029191</v>
       </c>
       <c r="F25">
-        <v>-3.035029706583683</v>
+        <v>-3.176742087456078</v>
       </c>
       <c r="G25">
-        <v>1.008814770422696</v>
+        <v>0.9177880102748958</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.587310398829163</v>
       </c>
       <c r="E26">
-        <v>-18.17773147700115</v>
+        <v>-20.01038679400932</v>
       </c>
       <c r="F26">
-        <v>-3.150019425691911</v>
+        <v>-3.950104486760088</v>
       </c>
       <c r="G26">
-        <v>0.6054777651911306</v>
+        <v>0.6254072493375431</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-3.134494279898498</v>
       </c>
       <c r="E27">
-        <v>-18.24350756196257</v>
+        <v>-21.55918830326869</v>
       </c>
       <c r="F27">
-        <v>-2.738416633828071</v>
+        <v>-3.553203236909273</v>
       </c>
       <c r="G27">
-        <v>0.2971567274821871</v>
+        <v>0.1522210437728945</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.646428684843238</v>
       </c>
       <c r="E28">
-        <v>-18.91688258995513</v>
+        <v>-21.29555866043815</v>
       </c>
       <c r="F28">
-        <v>-2.82902124110332</v>
+        <v>-3.413331914163577</v>
       </c>
       <c r="G28">
-        <v>-0.275100863890691</v>
+        <v>-0.4767097766867671</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-4.089197373923232</v>
       </c>
       <c r="E29">
-        <v>-19.45115648185409</v>
+        <v>-19.97165022734771</v>
       </c>
       <c r="F29">
-        <v>-2.875107083242608</v>
+        <v>-3.470169535762783</v>
       </c>
       <c r="G29">
-        <v>-0.02114891557319826</v>
+        <v>-0.05109611052144541</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.435417245292454</v>
       </c>
       <c r="E30">
-        <v>-19.23971750196195</v>
+        <v>-20.66687061395327</v>
       </c>
       <c r="F30">
-        <v>-2.929860547857096</v>
+        <v>-4.061696364826741</v>
       </c>
       <c r="G30">
-        <v>-0.5911950625258432</v>
+        <v>0.1455999526943522</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.667648768525272</v>
       </c>
       <c r="E31">
-        <v>-19.07237680195651</v>
+        <v>-20.42815210663893</v>
       </c>
       <c r="F31">
-        <v>-3.069588545217445</v>
+        <v>-3.558653560817258</v>
       </c>
       <c r="G31">
-        <v>-0.7610194275993766</v>
+        <v>-0.02595913824175929</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.782672346761471</v>
       </c>
       <c r="E32">
-        <v>-17.84303649156825</v>
+        <v>-20.30822000101979</v>
       </c>
       <c r="F32">
-        <v>-2.691720273058381</v>
+        <v>-3.943662762949038</v>
       </c>
       <c r="G32">
-        <v>-0.5648696043975587</v>
+        <v>-0.3022440267671755</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.783125749796485</v>
       </c>
       <c r="E33">
-        <v>-18.42127280913367</v>
+        <v>-20.92884736377101</v>
       </c>
       <c r="F33">
-        <v>-3.189219314510868</v>
+        <v>-4.018796938989317</v>
       </c>
       <c r="G33">
-        <v>-0.1019825060055828</v>
+        <v>-0.3504058432724927</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-4.680005559155411</v>
       </c>
       <c r="E34">
-        <v>-18.89940720875953</v>
+        <v>-19.42522643968617</v>
       </c>
       <c r="F34">
-        <v>-3.322523800678195</v>
+        <v>-3.658791285850495</v>
       </c>
       <c r="G34">
-        <v>0.374563903281426</v>
+        <v>-0.4653413633049098</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.487702924880568</v>
       </c>
       <c r="E35">
-        <v>-18.020009255788</v>
+        <v>-19.16441803616241</v>
       </c>
       <c r="F35">
-        <v>-3.315561037620965</v>
+        <v>-4.07749699874508</v>
       </c>
       <c r="G35">
-        <v>0.7789966990864906</v>
+        <v>0.03806019139666692</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.221218470226162</v>
       </c>
       <c r="E36">
-        <v>-17.23527452347281</v>
+        <v>-18.84930417233867</v>
       </c>
       <c r="F36">
-        <v>-3.085665535818029</v>
+        <v>-3.590887519167155</v>
       </c>
       <c r="G36">
-        <v>0.6934290285329482</v>
+        <v>-0.2480503962893061</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.898758175942525</v>
       </c>
       <c r="E37">
-        <v>-17.85034544861663</v>
+        <v>-18.855992728448</v>
       </c>
       <c r="F37">
-        <v>-3.524195287509127</v>
+        <v>-4.022483014507502</v>
       </c>
       <c r="G37">
-        <v>1.439937184365365</v>
+        <v>0.8493557234326211</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.534278959978706</v>
       </c>
       <c r="E38">
-        <v>-16.46367689425388</v>
+        <v>-17.92582605337648</v>
       </c>
       <c r="F38">
-        <v>-3.281655477677322</v>
+        <v>-3.763390310447524</v>
       </c>
       <c r="G38">
-        <v>1.998528843752132</v>
+        <v>0.2418805486129761</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.140541824831798</v>
       </c>
       <c r="E39">
-        <v>-16.68810353760001</v>
+        <v>-18.70505868977234</v>
       </c>
       <c r="F39">
-        <v>-3.588051101872603</v>
+        <v>-4.012047976230671</v>
       </c>
       <c r="G39">
-        <v>1.338280262490965</v>
+        <v>1.694769737796304</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.727064235029077</v>
       </c>
       <c r="E40">
-        <v>-16.38222776075192</v>
+        <v>-17.72850232696625</v>
       </c>
       <c r="F40">
-        <v>-3.452197641034377</v>
+        <v>-3.498644568122385</v>
       </c>
       <c r="G40">
-        <v>1.928467768504536</v>
+        <v>0.7067970114205252</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-2.298776002999126</v>
       </c>
       <c r="E41">
-        <v>-16.11207711535033</v>
+        <v>-17.57079369117512</v>
       </c>
       <c r="F41">
-        <v>-3.667642618211886</v>
+        <v>-4.366294482807998</v>
       </c>
       <c r="G41">
-        <v>2.036014150893299</v>
+        <v>1.198403092365679</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.86259370327274</v>
       </c>
       <c r="E42">
-        <v>-16.2803144532093</v>
+        <v>-17.31357636753944</v>
       </c>
       <c r="F42">
-        <v>-3.449125251558424</v>
+        <v>-4.469879935619146</v>
       </c>
       <c r="G42">
-        <v>1.364029685695416</v>
+        <v>0.9588950542360262</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.422969366774454</v>
       </c>
       <c r="E43">
-        <v>-15.78444654936939</v>
+        <v>-16.25204318997941</v>
       </c>
       <c r="F43">
-        <v>-3.397380036330313</v>
+        <v>-3.749724512103197</v>
       </c>
       <c r="G43">
-        <v>2.186971716938527</v>
+        <v>1.911944835718033</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-0.9870479076644967</v>
       </c>
       <c r="E44">
-        <v>-14.77898493697234</v>
+        <v>-15.06715438045044</v>
       </c>
       <c r="F44">
-        <v>-3.29505362972194</v>
+        <v>-4.001521874863704</v>
       </c>
       <c r="G44">
-        <v>2.80780825355467</v>
+        <v>1.419696508938261</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-0.5642057460321145</v>
       </c>
       <c r="E45">
-        <v>-14.61530324396509</v>
+        <v>-15.06314215247964</v>
       </c>
       <c r="F45">
-        <v>-3.50748402268941</v>
+        <v>-4.294212108066771</v>
       </c>
       <c r="G45">
-        <v>3.128245887937346</v>
+        <v>1.858515941259736</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1631114492289983</v>
       </c>
       <c r="E46">
-        <v>-14.87849815329089</v>
+        <v>-14.73261336313379</v>
       </c>
       <c r="F46">
-        <v>-3.321396993919359</v>
+        <v>-4.001490200745394</v>
       </c>
       <c r="G46">
-        <v>2.209450321150178</v>
+        <v>2.071566099439533</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>0.202578361713158</v>
       </c>
       <c r="E47">
-        <v>-14.36955201651683</v>
+        <v>-15.31210859647334</v>
       </c>
       <c r="F47">
-        <v>-3.893544805549042</v>
+        <v>-4.435584784020305</v>
       </c>
       <c r="G47">
-        <v>3.005792118985244</v>
+        <v>2.123548285497169</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>0.5217485202313302</v>
       </c>
       <c r="E48">
-        <v>-13.72012355907683</v>
+        <v>-15.59988859118679</v>
       </c>
       <c r="F48">
-        <v>-3.691170153291654</v>
+        <v>-4.029389556004734</v>
       </c>
       <c r="G48">
-        <v>3.119350452073324</v>
+        <v>2.317784613377288</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>0.7833820411365745</v>
       </c>
       <c r="E49">
-        <v>-13.40246016438677</v>
+        <v>-14.89353721547036</v>
       </c>
       <c r="F49">
-        <v>-4.072935133855657</v>
+        <v>-4.439939183434806</v>
       </c>
       <c r="G49">
-        <v>3.110915182039261</v>
+        <v>2.02147423488482</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>0.9779777921661177</v>
       </c>
       <c r="E50">
-        <v>-13.82215913541766</v>
+        <v>-13.37233675528775</v>
       </c>
       <c r="F50">
-        <v>-3.951511609465956</v>
+        <v>-4.431486153111147</v>
       </c>
       <c r="G50">
-        <v>2.822917583395903</v>
+        <v>2.28743022132771</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>1.101929299131149</v>
       </c>
       <c r="E51">
-        <v>-12.51262860730157</v>
+        <v>-13.88143686017806</v>
       </c>
       <c r="F51">
-        <v>-3.824403372692786</v>
+        <v>-4.461203602761411</v>
       </c>
       <c r="G51">
-        <v>2.957961357033854</v>
+        <v>2.288774302816655</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>1.151515082752402</v>
       </c>
       <c r="E52">
-        <v>-13.15450809857079</v>
+        <v>-12.41632155058044</v>
       </c>
       <c r="F52">
-        <v>-3.903241836869277</v>
+        <v>-4.048588030964648</v>
       </c>
       <c r="G52">
-        <v>3.602484846983483</v>
+        <v>1.293385954432908</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>1.128957629610891</v>
       </c>
       <c r="E53">
-        <v>-13.7015115309053</v>
+        <v>-13.12584738657624</v>
       </c>
       <c r="F53">
-        <v>-4.180874194228347</v>
+        <v>-4.753213634273798</v>
       </c>
       <c r="G53">
-        <v>3.786859059702113</v>
+        <v>3.250309012515814</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>1.038417909806055</v>
       </c>
       <c r="E54">
-        <v>-11.78195026921594</v>
+        <v>-13.31669086668149</v>
       </c>
       <c r="F54">
-        <v>-4.215473417362953</v>
+        <v>-4.581515365598473</v>
       </c>
       <c r="G54">
-        <v>3.820957678756606</v>
+        <v>2.062743495577375</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>0.8858773384597457</v>
       </c>
       <c r="E55">
-        <v>-12.58247126192187</v>
+        <v>-11.96125066907564</v>
       </c>
       <c r="F55">
-        <v>-4.61283948489995</v>
+        <v>-4.614559389524117</v>
       </c>
       <c r="G55">
-        <v>3.675432717941324</v>
+        <v>2.692647616425583</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>0.6817758370541096</v>
       </c>
       <c r="E56">
-        <v>-11.41383061713242</v>
+        <v>-12.10831286247473</v>
       </c>
       <c r="F56">
-        <v>-4.095758711656012</v>
+        <v>-4.548558445498178</v>
       </c>
       <c r="G56">
-        <v>3.432518128451761</v>
+        <v>2.786117559181365</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>0.4354412301004754</v>
       </c>
       <c r="E57">
-        <v>-11.59770930421387</v>
+        <v>-10.60966873132432</v>
       </c>
       <c r="F57">
-        <v>-4.555267815608937</v>
+        <v>-4.858287770645459</v>
       </c>
       <c r="G57">
-        <v>3.081951219116178</v>
+        <v>2.611585598350988</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>0.1590442794756462</v>
       </c>
       <c r="E58">
-        <v>-12.05358625409204</v>
+        <v>-11.68143626014169</v>
       </c>
       <c r="F58">
-        <v>-4.599121424260413</v>
+        <v>-4.170268115712649</v>
       </c>
       <c r="G58">
-        <v>3.416607646590023</v>
+        <v>1.337426141741833</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-0.1361094882198917</v>
       </c>
       <c r="E59">
-        <v>-11.92189370147498</v>
+        <v>-10.6188071918718</v>
       </c>
       <c r="F59">
-        <v>-4.304899747437115</v>
+        <v>-4.6925046435643</v>
       </c>
       <c r="G59">
-        <v>4.109686907964143</v>
+        <v>1.814277121218455</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-0.4394449451893324</v>
       </c>
       <c r="E60">
-        <v>-11.49813721773321</v>
+        <v>-10.37684176869396</v>
       </c>
       <c r="F60">
-        <v>-4.280752191491452</v>
+        <v>-4.511366695779998</v>
       </c>
       <c r="G60">
-        <v>3.445869558611641</v>
+        <v>1.604603719488714</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.7409474276243144</v>
       </c>
       <c r="E61">
-        <v>-11.20670274449558</v>
+        <v>-11.5747001277809</v>
       </c>
       <c r="F61">
-        <v>-4.09132512694574</v>
+        <v>-4.625095784979536</v>
       </c>
       <c r="G61">
-        <v>3.501943578955817</v>
+        <v>2.276498799957037</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-1.033453628358768</v>
       </c>
       <c r="E62">
-        <v>-11.627307410328</v>
+        <v>-11.32110558335136</v>
       </c>
       <c r="F62">
-        <v>-4.226079495878651</v>
+        <v>-4.322851053988621</v>
       </c>
       <c r="G62">
-        <v>3.557560744015573</v>
+        <v>2.194973305506945</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.310043739424385</v>
       </c>
       <c r="E63">
-        <v>-10.6878845343848</v>
+        <v>-9.656049089367075</v>
       </c>
       <c r="F63">
-        <v>-4.241426398052217</v>
+        <v>-4.735009726628779</v>
       </c>
       <c r="G63">
-        <v>3.858456228079931</v>
+        <v>1.393106207166835</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-1.565201757837839</v>
       </c>
       <c r="E64">
-        <v>-11.38163769541189</v>
+        <v>-12.16842382645255</v>
       </c>
       <c r="F64">
-        <v>-4.300095575542629</v>
+        <v>-5.061014797469032</v>
       </c>
       <c r="G64">
-        <v>2.627161715113259</v>
+        <v>0.808165915833009</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-1.793518113532744</v>
       </c>
       <c r="E65">
-        <v>-11.34899192629059</v>
+        <v>-10.40655761513229</v>
       </c>
       <c r="F65">
-        <v>-4.214375909163554</v>
+        <v>-4.394595307516901</v>
       </c>
       <c r="G65">
-        <v>2.766585340499665</v>
+        <v>0.3939868739603301</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-1.989305862175594</v>
       </c>
       <c r="E66">
-        <v>-11.24084291003941</v>
+        <v>-9.972974342793885</v>
       </c>
       <c r="F66">
-        <v>-4.025827801400911</v>
+        <v>-4.449359858072797</v>
       </c>
       <c r="G66">
-        <v>2.567406368129414</v>
+        <v>0.9112331301071389</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.147372700147174</v>
       </c>
       <c r="E67">
-        <v>-10.41890676375121</v>
+        <v>-11.53802854526678</v>
       </c>
       <c r="F67">
-        <v>-4.354606733152055</v>
+        <v>-5.132278396251976</v>
       </c>
       <c r="G67">
-        <v>2.561523528706129</v>
+        <v>0.420160046993808</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.262285135470861</v>
       </c>
       <c r="E68">
-        <v>-11.11980132828839</v>
+        <v>-10.42715311491918</v>
       </c>
       <c r="F68">
-        <v>-4.513884788185546</v>
+        <v>-4.620954394010661</v>
       </c>
       <c r="G68">
-        <v>1.658843697604133</v>
+        <v>0.9820556308287673</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.32844897431605</v>
       </c>
       <c r="E69">
-        <v>-10.99386446613507</v>
+        <v>-9.272324315853119</v>
       </c>
       <c r="F69">
-        <v>-4.727281241761434</v>
+        <v>-4.85138043729527</v>
       </c>
       <c r="G69">
-        <v>2.266159966237893</v>
+        <v>-0.3138143834269283</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.340585272752291</v>
       </c>
       <c r="E70">
-        <v>-10.9498386418325</v>
+        <v>-9.116911616383881</v>
       </c>
       <c r="F70">
-        <v>-4.366927965174174</v>
+        <v>-4.899677132892512</v>
       </c>
       <c r="G70">
-        <v>2.138740378976884</v>
+        <v>0.4247319103835416</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.294486225583176</v>
       </c>
       <c r="E71">
-        <v>-11.71118833437208</v>
+        <v>-9.985681240859407</v>
       </c>
       <c r="F71">
-        <v>-4.544809813596332</v>
+        <v>-4.440670855567738</v>
       </c>
       <c r="G71">
-        <v>1.335949638431318</v>
+        <v>0.3436963766732615</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.18837694878516</v>
       </c>
       <c r="E72">
-        <v>-12.01603161914643</v>
+        <v>-10.78132506705907</v>
       </c>
       <c r="F72">
-        <v>-4.076004355919778</v>
+        <v>-4.648228977286359</v>
       </c>
       <c r="G72">
-        <v>1.763341067551228</v>
+        <v>-0.6973775001524273</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.023693528126611</v>
       </c>
       <c r="E73">
-        <v>-11.54165585294693</v>
+        <v>-10.35291331203743</v>
       </c>
       <c r="F73">
-        <v>-4.208619138160931</v>
+        <v>-4.590375408342399</v>
       </c>
       <c r="G73">
-        <v>1.657380436475775</v>
+        <v>0.2125590467716512</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.804697792948026</v>
       </c>
       <c r="E74">
-        <v>-12.20666678944733</v>
+        <v>-11.38020216915146</v>
       </c>
       <c r="F74">
-        <v>-4.356489759485513</v>
+        <v>-5.062435381675181</v>
       </c>
       <c r="G74">
-        <v>1.159126780087765</v>
+        <v>0.4619589949726461</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.538574824123385</v>
       </c>
       <c r="E75">
-        <v>-11.98316395479876</v>
+        <v>-11.82776936922555</v>
       </c>
       <c r="F75">
-        <v>-4.37826413211689</v>
+        <v>-4.84655013425318</v>
       </c>
       <c r="G75">
-        <v>0.817809534988906</v>
+        <v>0.02907868134862419</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.234178397019156</v>
       </c>
       <c r="E76">
-        <v>-12.51802654831871</v>
+        <v>-11.67558547172378</v>
       </c>
       <c r="F76">
-        <v>-4.653692762694625</v>
+        <v>-4.845438372700541</v>
       </c>
       <c r="G76">
-        <v>0.9287790214652761</v>
+        <v>0.6633096852166589</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.9019592538776195</v>
       </c>
       <c r="E77">
-        <v>-12.38427354002816</v>
+        <v>-11.85626705615582</v>
       </c>
       <c r="F77">
-        <v>-4.483468132373616</v>
+        <v>-4.997781379530323</v>
       </c>
       <c r="G77">
-        <v>0.8039582124525954</v>
+        <v>-0.02962391215373249</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.5533058539481596</v>
       </c>
       <c r="E78">
-        <v>-12.90151584118427</v>
+        <v>-12.14221754737016</v>
       </c>
       <c r="F78">
-        <v>-4.518704797139186</v>
+        <v>-4.982187419233949</v>
       </c>
       <c r="G78">
-        <v>1.642039368446793</v>
+        <v>-0.07039328046985717</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.1996097476890892</v>
       </c>
       <c r="E79">
-        <v>-12.67061348000716</v>
+        <v>-12.02854379282962</v>
       </c>
       <c r="F79">
-        <v>-4.692609168154719</v>
+        <v>-4.490034968951986</v>
       </c>
       <c r="G79">
-        <v>1.057208325115763</v>
+        <v>0.5262332366175961</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>0.1481149902580542</v>
       </c>
       <c r="E80">
-        <v>-14.03720730909391</v>
+        <v>-13.40457043327434</v>
       </c>
       <c r="F80">
-        <v>-4.587639556373477</v>
+        <v>-4.709097922293317</v>
       </c>
       <c r="G80">
-        <v>0.9645858820180333</v>
+        <v>0.4541759024098195</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.4802003584325459</v>
       </c>
       <c r="E81">
-        <v>-13.81549322167837</v>
+        <v>-14.37870859096035</v>
       </c>
       <c r="F81">
-        <v>-4.655534612674281</v>
+        <v>-4.986990007422519</v>
       </c>
       <c r="G81">
-        <v>0.5336488586255637</v>
+        <v>0.1540848809115042</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.7884027369267324</v>
       </c>
       <c r="E82">
-        <v>-15.20578002677324</v>
+        <v>-15.58830022620116</v>
       </c>
       <c r="F82">
-        <v>-4.746570779811488</v>
+        <v>-5.650733034377557</v>
       </c>
       <c r="G82">
-        <v>1.678557996290493</v>
+        <v>-1.028773040270091</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>1.066337874103139</v>
       </c>
       <c r="E83">
-        <v>-14.39240722483355</v>
+        <v>-15.57946064493819</v>
       </c>
       <c r="F83">
-        <v>-4.781662535485794</v>
+        <v>-5.771435972575732</v>
       </c>
       <c r="G83">
-        <v>0.8118803479280713</v>
+        <v>-0.3608936515409038</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>1.309743009009443</v>
       </c>
       <c r="E84">
-        <v>-16.61910770761915</v>
+        <v>-16.08233862654196</v>
       </c>
       <c r="F84">
-        <v>-4.807771511207729</v>
+        <v>-5.500311854676161</v>
       </c>
       <c r="G84">
-        <v>0.5748750822261077</v>
+        <v>-0.9006052697172069</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.515660501207938</v>
       </c>
       <c r="E85">
-        <v>-17.55379832822433</v>
+        <v>-16.66252218793068</v>
       </c>
       <c r="F85">
-        <v>-4.938823967563302</v>
+        <v>-5.508290565078145</v>
       </c>
       <c r="G85">
-        <v>0.5238827492847137</v>
+        <v>-0.9750793021686516</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.682352354763513</v>
       </c>
       <c r="E86">
-        <v>-18.17552611015942</v>
+        <v>-18.48530543160213</v>
       </c>
       <c r="F86">
-        <v>-5.016916506253621</v>
+        <v>-5.57307047184328</v>
       </c>
       <c r="G86">
-        <v>0.8887147993490162</v>
+        <v>-0.7444600788119421</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.808967780322729</v>
       </c>
       <c r="E87">
-        <v>-20.89105271970299</v>
+        <v>-19.46742276048964</v>
       </c>
       <c r="F87">
-        <v>-5.057353269392536</v>
+        <v>-5.494234383225661</v>
       </c>
       <c r="G87">
-        <v>0.03828530849333736</v>
+        <v>-1.056584933345508</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.89514406948955</v>
       </c>
       <c r="E88">
-        <v>-20.71196515812165</v>
+        <v>-19.8163145119366</v>
       </c>
       <c r="F88">
-        <v>-4.767558050602891</v>
+        <v>-5.680191548110646</v>
       </c>
       <c r="G88">
-        <v>0.08755284720877117</v>
+        <v>-0.7455095217478911</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.941035534872417</v>
       </c>
       <c r="E89">
-        <v>-23.55861373255733</v>
+        <v>-23.8231490701894</v>
       </c>
       <c r="F89">
-        <v>-5.134456783738663</v>
+        <v>-5.647278971775983</v>
       </c>
       <c r="G89">
-        <v>-0.3546433415627598</v>
+        <v>-0.4598524788007982</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.947702872217004</v>
       </c>
       <c r="E90">
-        <v>-24.12226383534404</v>
+        <v>-24.24919243330503</v>
       </c>
       <c r="F90">
-        <v>-4.856455422901296</v>
+        <v>-5.620332215624781</v>
       </c>
       <c r="G90">
-        <v>-0.03302715296810328</v>
+        <v>-0.6527116197365804</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.917083807250802</v>
       </c>
       <c r="E91">
-        <v>-26.13897444991996</v>
+        <v>-25.65376657389411</v>
       </c>
       <c r="F91">
-        <v>-5.096923745395705</v>
+        <v>-5.756427191615113</v>
       </c>
       <c r="G91">
-        <v>-0.4790701956562674</v>
+        <v>-0.6662318877189639</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>1.850537484943019</v>
       </c>
       <c r="E92">
-        <v>-27.31438516335087</v>
+        <v>-27.44490936967396</v>
       </c>
       <c r="F92">
-        <v>-5.2351638510485</v>
+        <v>-5.752589872182003</v>
       </c>
       <c r="G92">
-        <v>-0.6262702925144215</v>
+        <v>-1.492401700862864</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>1.747652315391199</v>
       </c>
       <c r="E93">
-        <v>-29.45957311399841</v>
+        <v>-29.24841942796875</v>
       </c>
       <c r="F93">
-        <v>-5.387477559318846</v>
+        <v>-5.185775190222563</v>
       </c>
       <c r="G93">
-        <v>-0.7914003040132682</v>
+        <v>-1.473452138196075</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>1.605420470072023</v>
       </c>
       <c r="E94">
-        <v>-31.87592382398824</v>
+        <v>-32.05052819630198</v>
       </c>
       <c r="F94">
-        <v>-5.153732860288434</v>
+        <v>-5.474993940058988</v>
       </c>
       <c r="G94">
-        <v>-1.509669506395702</v>
+        <v>-2.13235001687722</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>1.420682436069228</v>
       </c>
       <c r="E95">
-        <v>-33.56156223233738</v>
+        <v>-32.49066643476649</v>
       </c>
       <c r="F95">
-        <v>-5.091851927201511</v>
+        <v>-5.326924563642019</v>
       </c>
       <c r="G95">
-        <v>-1.294196028881158</v>
+        <v>-2.912698569212067</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>1.182281462240687</v>
       </c>
       <c r="E96">
-        <v>-36.07575741597394</v>
+        <v>-35.18219439630642</v>
       </c>
       <c r="F96">
-        <v>-4.75867900338798</v>
+        <v>-5.744392610363688</v>
       </c>
       <c r="G96">
-        <v>-1.465218811439908</v>
+        <v>-2.850695361807057</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>0.8924251792354646</v>
       </c>
       <c r="E97">
-        <v>-37.72866627843265</v>
+        <v>-38.16832449865235</v>
       </c>
       <c r="F97">
-        <v>-5.064063431356253</v>
+        <v>-5.276639525267943</v>
       </c>
       <c r="G97">
-        <v>-1.735766524545767</v>
+        <v>-3.099529206720836</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>0.5299422624408542</v>
       </c>
       <c r="E98">
-        <v>-41.25179414979314</v>
+        <v>-39.13258379029061</v>
       </c>
       <c r="F98">
-        <v>-4.686589501970134</v>
+        <v>-5.412595926990674</v>
       </c>
       <c r="G98">
-        <v>-2.49469253669599</v>
+        <v>-3.736812533576079</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.1153556702079404</v>
       </c>
       <c r="E99">
-        <v>-44.28821522023125</v>
+        <v>-43.80957815999054</v>
       </c>
       <c r="F99">
-        <v>-4.763590867284715</v>
+        <v>-5.599671980104916</v>
       </c>
       <c r="G99">
-        <v>-2.910288492059477</v>
+        <v>-3.878503882656886</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-0.3900657681752997</v>
       </c>
       <c r="E100">
-        <v>-45.19180880982577</v>
+        <v>-45.61672458291349</v>
       </c>
       <c r="F100">
-        <v>-4.814330429256522</v>
+        <v>-4.997929456033417</v>
       </c>
       <c r="G100">
-        <v>-2.586037109215561</v>
+        <v>-4.013822431574596</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.9211516404102494</v>
       </c>
       <c r="E101">
-        <v>-47.96193070200582</v>
+        <v>-46.81858611302321</v>
       </c>
       <c r="F101">
-        <v>-4.894268777191286</v>
+        <v>-5.18654012017972</v>
       </c>
       <c r="G101">
-        <v>-3.585007467872799</v>
+        <v>-4.584937884736425</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-1.574133462755815</v>
       </c>
       <c r="E102">
-        <v>-49.86872506334905</v>
+        <v>-49.26787128235232</v>
       </c>
       <c r="F102">
-        <v>-4.541340705788563</v>
+        <v>-4.618882114820309</v>
       </c>
       <c r="G102">
-        <v>-3.908553704516851</v>
+        <v>-5.09506977851934</v>
       </c>
     </row>
   </sheetData>
